--- a/Thesis/data/raw/autoic/coded-Harris_Longitudinal.xlsx
+++ b/Thesis/data/raw/autoic/coded-Harris_Longitudinal.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kathrene.conway\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b4dcdb2932ef22e/Documents/Integrative-Data-Project/Thesis/data/raw/autoic/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_23289518730CCCB08BF04F20856447B18ADDCD2A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F948D0FF-33DB-44BC-9F3A-34D6A3E92FAC}"/>
   <bookViews>
-    <workbookView xWindow="190" yWindow="0" windowWidth="19030" windowHeight="8700" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paragraph" sheetId="1" r:id="rId1"/>
@@ -478,7 +479,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -523,11 +524,11 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -549,9 +550,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -589,9 +590,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -626,7 +627,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -661,7 +662,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -834,20 +835,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:N100"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.90625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="56.36328125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.453125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.90625" style="1"/>
+    <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="56.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -891,7 +892,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -935,7 +936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -979,7 +980,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
@@ -1023,7 +1024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
@@ -1067,7 +1068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
@@ -1111,7 +1112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
@@ -1155,7 +1156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
@@ -1199,7 +1200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
@@ -1243,7 +1244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>32</v>
       </c>
@@ -1287,7 +1288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -1331,7 +1332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
@@ -1375,7 +1376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -1419,7 +1420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
@@ -1463,7 +1464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
@@ -1507,7 +1508,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
@@ -1551,7 +1552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -1595,7 +1596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>33</v>
       </c>
@@ -1639,7 +1640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>33</v>
       </c>
@@ -1683,7 +1684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>34</v>
       </c>
@@ -1727,7 +1728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>34</v>
       </c>
@@ -1771,7 +1772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>34</v>
       </c>
@@ -1815,7 +1816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
@@ -1859,7 +1860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
@@ -1903,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -1947,7 +1948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -1991,7 +1992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
@@ -2035,7 +2036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -2079,7 +2080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -2123,7 +2124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>35</v>
       </c>
@@ -2167,7 +2168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>35</v>
       </c>
@@ -2211,7 +2212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
@@ -2255,7 +2256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
@@ -2299,7 +2300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -2343,7 +2344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -2387,7 +2388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>36</v>
       </c>
@@ -2431,7 +2432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -2475,7 +2476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
@@ -2519,7 +2520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
@@ -2563,7 +2564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>37</v>
       </c>
@@ -2607,7 +2608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>37</v>
       </c>
@@ -2651,7 +2652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>37</v>
       </c>
@@ -2695,7 +2696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>38</v>
       </c>
@@ -2739,7 +2740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>38</v>
       </c>
@@ -2783,7 +2784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2827,7 +2828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>38</v>
       </c>
@@ -2871,7 +2872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>38</v>
       </c>
@@ -2915,7 +2916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>39</v>
       </c>
@@ -2959,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>39</v>
       </c>
@@ -3003,7 +3004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>39</v>
       </c>
@@ -3047,7 +3048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -3091,7 +3092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>40</v>
       </c>
@@ -3135,7 +3136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>40</v>
       </c>
@@ -3179,7 +3180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>40</v>
       </c>
@@ -3223,7 +3224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>40</v>
       </c>
@@ -3267,7 +3268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>40</v>
       </c>
@@ -3311,7 +3312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>41</v>
       </c>
@@ -3355,7 +3356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>41</v>
       </c>
@@ -3399,7 +3400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>41</v>
       </c>
@@ -3443,7 +3444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>41</v>
       </c>
@@ -3487,7 +3488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>41</v>
       </c>
@@ -3531,7 +3532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>41</v>
       </c>
@@ -3575,7 +3576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>42</v>
       </c>
@@ -3619,7 +3620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>42</v>
       </c>
@@ -3663,7 +3664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>42</v>
       </c>
@@ -3707,7 +3708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>43</v>
       </c>
@@ -3751,7 +3752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>43</v>
       </c>
@@ -3795,7 +3796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>43</v>
       </c>
@@ -3839,7 +3840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>44</v>
       </c>
@@ -3883,7 +3884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>44</v>
       </c>
@@ -3927,7 +3928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>44</v>
       </c>
@@ -3971,7 +3972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>44</v>
       </c>
@@ -4015,7 +4016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>45</v>
       </c>
@@ -4059,7 +4060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>45</v>
       </c>
@@ -4103,7 +4104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>45</v>
       </c>
@@ -4147,7 +4148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>45</v>
       </c>
@@ -4191,7 +4192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>45</v>
       </c>
@@ -4235,7 +4236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>45</v>
       </c>
@@ -4279,7 +4280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>45</v>
       </c>
@@ -4323,7 +4324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>45</v>
       </c>
@@ -4367,7 +4368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>45</v>
       </c>
@@ -4411,7 +4412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>45</v>
       </c>
@@ -4455,7 +4456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>45</v>
       </c>
@@ -4499,7 +4500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>45</v>
       </c>
@@ -4543,7 +4544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>45</v>
       </c>
@@ -4587,7 +4588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>46</v>
       </c>
@@ -4631,7 +4632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>46</v>
       </c>
@@ -4675,7 +4676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>46</v>
       </c>
@@ -4719,7 +4720,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>46</v>
       </c>
@@ -4763,7 +4764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>46</v>
       </c>
@@ -4807,7 +4808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>47</v>
       </c>
@@ -4851,7 +4852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>47</v>
       </c>
@@ -4895,7 +4896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>47</v>
       </c>
@@ -4939,7 +4940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>47</v>
       </c>
@@ -4983,7 +4984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>47</v>
       </c>
@@ -5027,7 +5028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>48</v>
       </c>
@@ -5071,7 +5072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>48</v>
       </c>
@@ -5115,7 +5116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>49</v>
       </c>
@@ -5159,7 +5160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>50</v>
       </c>
@@ -5203,7 +5204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>50</v>
       </c>
@@ -5248,7 +5249,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="1.25" right="1.25" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5258,38 +5259,38 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:Y21"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="22" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5366,7 +5367,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -5443,7 +5444,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -5520,7 +5521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -5597,7 +5598,7 @@
         <v>3.5714285714285712E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -5674,7 +5675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -5751,7 +5752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -5828,7 +5829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -5905,7 +5906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -5982,7 +5983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -6059,7 +6060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -6136,7 +6137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -6213,7 +6214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -6290,7 +6291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -6367,7 +6368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -6444,7 +6445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -6521,7 +6522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -6598,7 +6599,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -6675,7 +6676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -6752,7 +6753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -6765,6 +6766,33 @@
       <c r="D20">
         <v>0</v>
       </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
       <c r="N20">
         <v>1</v>
       </c>
@@ -6802,7 +6830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>50</v>
       </c>
